--- a/data/trans_dic/IP11C$urgencias-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP11C$urgencias-Provincia-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que a consecuencia del accidente necesitaron asistencia sanitaria y acudieron a un servicio de urgencias</t>
+          <t>Menores que a consecuencia del accidente necesitaron asistencia sanitaria y acudieron a un servicio de urgencias (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -638,7 +639,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -716,17 +717,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>26,32; 88,08</t>
+          <t>16,02; 87,87</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>21,33; 100,0</t>
+          <t>0,0; 100,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -736,49 +737,49 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>28,79; 89,28</t>
+          <t>36,02; 89,23</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>38,45; 100,0</t>
+          <t>49,86; 100,0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,55; 89,56</t>
+          <t>19,58; 89,03</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>55,59; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>39,98; 87,15</t>
+          <t>40,89; 86,47</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>36,91; 100,0</t>
+          <t>35,91; 100,0</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>31,13; 89,88</t>
+          <t>29,59; 87,79</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>33,5; 100,0</t>
+          <t>29,77; 100,0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -856,17 +857,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>63,75; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>28,17; 79,48</t>
+          <t>29,11; 79,89</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>79,25; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -876,49 +877,49 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>43,07; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>56,47; 94,67</t>
+          <t>56,55; 94,02</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>45,53; 100,0</t>
+          <t>51,32; 100,0</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>73,58; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>73,58; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>47,76; 84,09</t>
+          <t>50,9; 85,5</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>68,26; 100,0</t>
+          <t>67,2; 100,0</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>58,45; 100,0</t>
+          <t>62,06; 100,0</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -996,37 +997,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>31,66; 100,0</t>
+          <t>37,09; 100,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>23,86; 68,97</t>
+          <t>19,01; 68,48</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>22,85; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>43,28; 100,0</t>
+          <t>42,61; 100,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>19,98; 65,04</t>
+          <t>19,82; 60,91</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1036,12 +1037,12 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>56,08; 94,79</t>
+          <t>54,88; 94,64</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>26,59; 58,33</t>
+          <t>26,9; 57,75</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1051,7 +1052,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 79,69</t>
+          <t>0,0; 74,83</t>
         </is>
       </c>
     </row>
@@ -1136,57 +1137,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>27,3; 84,42</t>
+          <t>20,76; 84,1</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>63,75; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>38,12; 100,0</t>
+          <t>39,69; 100,0</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>22,85; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,26; 56,47</t>
+          <t>7,22; 55,32</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,29; 100,0</t>
+          <t>12,26; 100,0</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>55,04; 100,0</t>
+          <t>50,96; 100,0</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>20,97; 60,55</t>
+          <t>20,09; 58,97</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>29,39; 100,0</t>
+          <t>30,85; 100,0</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>66,07; 100,0</t>
+          <t>63,55; 100,0</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1276,7 +1277,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1286,7 +1287,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>22,85; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1306,39 +1307,39 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>43,07; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>43,07; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16,09; 84,29</t>
+          <t>16,25; 84,29</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>55,59; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>43,07; 100</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1416,69 +1417,69 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9,76; 68,58</t>
+          <t>10,23; 68,12</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>19,63; 100,0</t>
+          <t>20,0; 100,0</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>23,63; 100,0</t>
+          <t>25,82; 100,0</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 80,08</t>
+          <t>0,0; 80,13</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>32,59; 76,24</t>
+          <t>32,77; 76,24</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>14,31; 87,96</t>
+          <t>14,33; 88,12</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>55,59; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 64,78</t>
+          <t>0,0; 60,94</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>30,56; 68,12</t>
+          <t>30,95; 67,11</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>31,46; 85,07</t>
+          <t>31,75; 84,89</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>43,79; 100,0</t>
+          <t>39,44; 100,0</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1556,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>30,07; 90,22</t>
+          <t>30,03; 90,18</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>16,4; 59,59</t>
+          <t>12,04; 59,86</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>63,75; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>49,19; 100,0</t>
+          <t>48,47; 100,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>52,85; 93,78</t>
+          <t>52,87; 93,9</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>30,43; 67,71</t>
+          <t>31,38; 66,08</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>36,33; 100,0</t>
+          <t>34,39; 100,0</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>40,67; 100,0</t>
+          <t>35,81; 100,0</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>51,71; 85,46</t>
+          <t>50,21; 84,99</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>28,33; 57,09</t>
+          <t>30,01; 57,5</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>61,12; 100,0</t>
+          <t>52,42; 100,0</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>54,67; 96,05</t>
+          <t>55,61; 95,84</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>30,3; 100,0</t>
+          <t>37,06; 100,0</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>33,22; 89,81</t>
+          <t>33,32; 89,66</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>35,18; 100,0</t>
+          <t>33,72; 100,0</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>22,85; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>50,05; 94,39</t>
+          <t>48,04; 94,44</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>33,74; 100,0</t>
+          <t>34,73; 100,0</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>63,3; 100,0</t>
+          <t>63,38; 100,0</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>22,85; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>58,93; 94,9</t>
+          <t>57,11; 94,25</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>47,78; 93,68</t>
+          <t>47,39; 93,03</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>70,0; 100,0</t>
+          <t>65,13; 100,0</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>43,07; 100</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1836,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>47,21; 71,98</t>
+          <t>47,98; 73,73</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>38,36; 60,95</t>
+          <t>39,11; 61,49</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>74,54; 97,15</t>
+          <t>76,05; 97,36</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>46,66; 84,29</t>
+          <t>45,78; 84,98</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>51,93; 74,21</t>
+          <t>52,25; 74,66</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>46,34; 66,11</t>
+          <t>47,12; 65,87</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>61,69; 84,75</t>
+          <t>61,57; 84,73</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>62,43; 93,92</t>
+          <t>61,6; 93,85</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>53,35; 70,34</t>
+          <t>52,56; 69,97</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>45,56; 60,72</t>
+          <t>46,07; 60,94</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>69,61; 86,64</t>
+          <t>71,28; 87,94</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>62,36; 85,54</t>
+          <t>62,85; 87,22</t>
         </is>
       </c>
     </row>
@@ -1920,4 +1921,2040 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que a consecuencia del accidente necesitaron asistencia sanitaria y acudieron a un servicio de urgencias (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>2683</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1763</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>1422</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>5095</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>4399</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>3524</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>3804</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>7778</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>4399</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>5287</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>5226</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>736; 4040</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2380</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3145</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>2714; 6723</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>2582; 5178</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>1207; 5489</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>4961; 10491</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>2032; 5658</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>2528; 7501</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>2069; 6949</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>2419</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>5456</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>5353</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2259</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>1341</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>8288</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>5535</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>5109</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>3759</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>13743</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>10888</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>7368</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>2811; 7716</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>758; 2911</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>5770; 9593</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>3491; 6802</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>10109; 16981</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>8169; 12155</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>4977; 8020</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>4255</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>4929</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>759</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>5056</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>5516</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>1257</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>9311</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>10444</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>759</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>1257</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>2071; 5583</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>2152; 7754</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>2651; 6222</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>2721; 8363</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>0; 1966</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>6478; 11172</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>6738; 14468</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2226</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2874</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>3822</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2726</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>1865</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>2337</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>7016</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>5688</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>5062</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>11317</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>946</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>1419; 5746</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>1963; 4946</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>577; 4424</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>563; 4593</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>3992; 7834</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>2980; 8744</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>2258; 7318</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>8121; 12780</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>0; 2992</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Huelva</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>1399</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>605</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>653</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>1324</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>1043</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>2051</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>1930</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>1043</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>0; 2089</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>0; 1975</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>660; 3425</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>2954</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>2807</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>2701</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>659</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>7271</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>3069</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>2320</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>659</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>10226</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>5876</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>5022</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>806; 5366</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>709; 3545</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>894; 3462</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>0; 2575</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>4310; 10028</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>856; 5264</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>0; 2787</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>6509; 14114</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>3023; 8081</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>2281; 5783</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>4146</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>4147</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>2663</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>3581</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>8936</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>9912</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>3307</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>5285</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>13083</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>14059</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>5970</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>8866</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>2056; 6174</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>1440; 7156</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>1940; 4003</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>6177; 10970</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>6423; 13528</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>1346; 3915</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>2448; 6837</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>9303; 15748</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>9730; 18646</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>3448; 6578</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>6028; 10389</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>4082</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>3792</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>2639</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>810</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>6674</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>3396</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>6618</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>908</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>10755</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>7188</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>9257</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>1718</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>1807; 4875</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>1867; 5026</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>1051; 3118</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>4100; 8061</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>1415; 4075</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>4591; 7244</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>7658; 12638</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>4588; 9005</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>6749; 10362</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>21408</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>25402</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>20890</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>11718</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>29626</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>41772</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>30392</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>19726</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>51034</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>67174</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>51282</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>31444</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>16940; 26030</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>20223; 31799</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>17772; 22752</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>7852; 14574</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>24310; 34737</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>34579; 48331</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>25073; 34505</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>14805; 22556</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>43009; 57257</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>57634; 76231</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>45684; 56366</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>25883; 35922</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP11C$urgencias-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP11C$urgencias-Provincia-trans_dic.xlsx
@@ -737,17 +737,17 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>36,02; 89,23</t>
+          <t>34,64; 89,21</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>49,86; 100,0</t>
+          <t>37,63; 100,0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,58; 89,03</t>
+          <t>18,73; 89,51</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -757,22 +757,22 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>40,89; 86,47</t>
+          <t>39,24; 86,77</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>35,91; 100,0</t>
+          <t>37,71; 100,0</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>29,59; 87,79</t>
+          <t>28,18; 88,07</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>29,77; 100,0</t>
+          <t>29,9; 100,0</t>
         </is>
       </c>
     </row>
@@ -862,7 +862,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>29,11; 79,89</t>
+          <t>28,05; 79,42</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -882,12 +882,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>56,55; 94,02</t>
+          <t>59,51; 94,37</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>51,32; 100,0</t>
+          <t>42,34; 100,0</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -902,17 +902,17 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>50,9; 85,5</t>
+          <t>50,59; 84,27</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>67,2; 100,0</t>
+          <t>68,32; 100,0</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>62,06; 100,0</t>
+          <t>56,85; 100,0</t>
         </is>
       </c>
     </row>
@@ -997,12 +997,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>37,09; 100,0</t>
+          <t>37,93; 100,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>19,01; 68,48</t>
+          <t>18,76; 69,05</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1017,12 +1017,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>42,61; 100,0</t>
+          <t>41,67; 100,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>19,82; 60,91</t>
+          <t>20,11; 60,74</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1037,12 +1037,12 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>54,88; 94,64</t>
+          <t>56,02; 94,6</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>26,9; 57,75</t>
+          <t>27,04; 58,41</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 74,83</t>
+          <t>0,0; 71,58</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>20,76; 84,1</t>
+          <t>24,24; 84,13</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>39,69; 100,0</t>
+          <t>40,46; 100,0</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1157,17 +1157,17 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,22; 55,32</t>
+          <t>7,15; 56,12</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,26; 100,0</t>
+          <t>12,29; 100,0</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>50,96; 100,0</t>
+          <t>57,77; 100,0</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1177,17 +1177,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>20,09; 58,97</t>
+          <t>20,08; 60,91</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>30,85; 100,0</t>
+          <t>32,12; 100,0</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>63,55; 100,0</t>
+          <t>59,24; 100,0</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16,25; 84,29</t>
+          <t>16,19; 100,0</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1422,17 +1422,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>10,23; 68,12</t>
+          <t>9,88; 72,66</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>20,0; 100,0</t>
+          <t>17,82; 100,0</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>25,82; 100,0</t>
+          <t>25,45; 100,0</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1442,12 +1442,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>32,77; 76,24</t>
+          <t>32,4; 76,67</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>14,33; 88,12</t>
+          <t>13,31; 87,85</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1457,22 +1457,22 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 60,94</t>
+          <t>0,0; 58,5</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>30,95; 67,11</t>
+          <t>28,43; 65,89</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>31,75; 84,89</t>
+          <t>31,54; 84,94</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>39,44; 100,0</t>
+          <t>45,19; 100,0</t>
         </is>
       </c>
     </row>
@@ -1557,12 +1557,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>30,03; 90,18</t>
+          <t>29,96; 90,19</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>12,04; 59,86</t>
+          <t>16,36; 58,68</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1572,47 +1572,47 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>48,47; 100,0</t>
+          <t>46,31; 100,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>52,87; 93,9</t>
+          <t>52,86; 93,81</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>31,38; 66,08</t>
+          <t>30,66; 65,85</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>34,39; 100,0</t>
+          <t>35,08; 100,0</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>35,81; 100,0</t>
+          <t>39,79; 100,0</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>50,21; 84,99</t>
+          <t>50,24; 85,38</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>30,01; 57,5</t>
+          <t>29,8; 58,41</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>52,42; 100,0</t>
+          <t>61,7; 100,0</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>55,61; 95,84</t>
+          <t>54,19; 95,64</t>
         </is>
       </c>
     </row>
@@ -1697,17 +1697,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>37,06; 100,0</t>
+          <t>30,26; 100,0</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>33,32; 89,66</t>
+          <t>33,09; 89,63</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>33,72; 100,0</t>
+          <t>34,74; 100,0</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1717,17 +1717,17 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>48,04; 94,44</t>
+          <t>50,31; 94,17</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>34,73; 100,0</t>
+          <t>33,55; 100,0</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>63,38; 100,0</t>
+          <t>63,81; 100,0</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1737,17 +1737,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>57,11; 94,25</t>
+          <t>55,08; 94,32</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>47,39; 93,03</t>
+          <t>46,28; 93,31</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>65,13; 100,0</t>
+          <t>67,61; 100,0</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>47,98; 73,73</t>
+          <t>46,15; 72,55</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>39,11; 61,49</t>
+          <t>36,98; 60,1</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>76,05; 97,36</t>
+          <t>73,31; 96,93</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>45,78; 84,98</t>
+          <t>47,07; 85,19</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>52,25; 74,66</t>
+          <t>52,74; 74,34</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>47,12; 65,87</t>
+          <t>47,51; 66,18</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>61,57; 84,73</t>
+          <t>61,89; 84,78</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>61,6; 93,85</t>
+          <t>63,09; 93,49</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>52,56; 69,97</t>
+          <t>53,37; 70,18</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>46,07; 60,94</t>
+          <t>46,54; 60,79</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>71,28; 87,94</t>
+          <t>70,74; 87,58</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>62,85; 87,22</t>
+          <t>62,85; 87,16</t>
         </is>
       </c>
     </row>
@@ -2229,17 +2229,17 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2714; 6723</t>
+          <t>2610; 6722</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2582; 5178</t>
+          <t>1948; 5178</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1207; 5489</t>
+          <t>1155; 5518</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -2249,22 +2249,22 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>4961; 10491</t>
+          <t>4761; 10528</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2032; 5658</t>
+          <t>2134; 5658</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2528; 7501</t>
+          <t>2408; 7526</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2069; 6949</t>
+          <t>2078; 6949</t>
         </is>
       </c>
     </row>
@@ -2422,7 +2422,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2811; 7716</t>
+          <t>2709; 7670</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5770; 9593</t>
+          <t>6072; 9629</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3491; 6802</t>
+          <t>2880; 6802</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -2462,17 +2462,17 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>10109; 16981</t>
+          <t>10048; 16737</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8169; 12155</t>
+          <t>8305; 12155</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4977; 8020</t>
+          <t>4559; 8020</t>
         </is>
       </c>
     </row>
@@ -2625,12 +2625,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2071; 5583</t>
+          <t>2118; 5583</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2152; 7754</t>
+          <t>2124; 7818</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2651; 6222</t>
+          <t>2592; 6222</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2721; 8363</t>
+          <t>2761; 8339</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -2665,12 +2665,12 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>6478; 11172</t>
+          <t>6613; 11168</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6738; 14468</t>
+          <t>6772; 14632</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
@@ -2680,7 +2680,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0; 2874</t>
+          <t>0; 2749</t>
         </is>
       </c>
     </row>
@@ -2833,7 +2833,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1419; 5746</t>
+          <t>1656; 5748</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -2843,7 +2843,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1963; 4946</t>
+          <t>2001; 4946</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -2853,17 +2853,17 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>577; 4424</t>
+          <t>572; 4488</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>563; 4593</t>
+          <t>565; 4593</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3992; 7834</t>
+          <t>4526; 7834</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2873,17 +2873,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2980; 8744</t>
+          <t>2978; 9032</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2258; 7318</t>
+          <t>2351; 7318</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>8121; 12780</t>
+          <t>7571; 12780</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>660; 3425</t>
+          <t>658; 4063</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
@@ -3254,17 +3254,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>806; 5366</t>
+          <t>778; 5724</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>709; 3545</t>
+          <t>632; 3545</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>894; 3462</t>
+          <t>881; 3462</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4310; 10028</t>
+          <t>4261; 10083</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>856; 5264</t>
+          <t>795; 5248</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -3289,22 +3289,22 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 2787</t>
+          <t>0; 2675</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>6509; 14114</t>
+          <t>5979; 13858</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>3023; 8081</t>
+          <t>3002; 8086</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>2281; 5783</t>
+          <t>2613; 5783</t>
         </is>
       </c>
     </row>
@@ -3457,12 +3457,12 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2056; 6174</t>
+          <t>2051; 6174</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1440; 7156</t>
+          <t>1956; 7016</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -3472,47 +3472,47 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1940; 4003</t>
+          <t>1854; 4003</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>6177; 10970</t>
+          <t>6175; 10959</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6423; 13528</t>
+          <t>6276; 13481</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1346; 3915</t>
+          <t>1373; 3915</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>2448; 6837</t>
+          <t>2720; 6837</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>9303; 15748</t>
+          <t>9309; 15819</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>9730; 18646</t>
+          <t>9663; 18942</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3448; 6578</t>
+          <t>4058; 6578</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>6028; 10389</t>
+          <t>5875; 10367</t>
         </is>
       </c>
     </row>
@@ -3665,17 +3665,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>1807; 4875</t>
+          <t>1475; 4875</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1867; 5026</t>
+          <t>1855; 5024</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1051; 3118</t>
+          <t>1083; 3118</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -3685,17 +3685,17 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>4100; 8061</t>
+          <t>4294; 8038</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1415; 4075</t>
+          <t>1367; 4075</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>4591; 7244</t>
+          <t>4623; 7244</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3705,17 +3705,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>7658; 12638</t>
+          <t>7387; 12648</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>4588; 9005</t>
+          <t>4480; 9032</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>6749; 10362</t>
+          <t>7005; 10362</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>16940; 26030</t>
+          <t>16294; 25613</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>20223; 31799</t>
+          <t>19123; 31080</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>17772; 22752</t>
+          <t>17133; 22651</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>7852; 14574</t>
+          <t>8073; 14610</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>24310; 34737</t>
+          <t>24536; 34588</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>34579; 48331</t>
+          <t>34859; 48560</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>25073; 34505</t>
+          <t>25204; 34525</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>14805; 22556</t>
+          <t>15164; 22468</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>43009; 57257</t>
+          <t>43669; 57426</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>57634; 76231</t>
+          <t>58216; 76037</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>45684; 56366</t>
+          <t>45339; 56135</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>25883; 35922</t>
+          <t>25886; 35896</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP11C$urgencias-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP11C$urgencias-Provincia-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>67,61%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>84,95%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>57,16%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>58,36%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>74,07%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>45,21%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>67,61%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>84,95%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>57,16%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>44,49%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>75,2%</t>
+          <t>72,4%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>16,02; 87,87</t>
+          <t>28,79; 89,28</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>38,45; 100,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
+          <t>18,55; 89,56</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>26,32; 88,08</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>21,33; 100,0</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>0,0; 100,0</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 100,0</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>34,64; 89,21</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>37,63; 100,0</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>18,73; 89,51</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>39,24; 86,77</t>
+          <t>39,98; 87,15</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>37,71; 100,0</t>
+          <t>36,91; 100,0</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>28,18; 88,07</t>
+          <t>31,13; 89,88</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>29,9; 100,0</t>
+          <t>29,29; 100,0</t>
         </is>
       </c>
     </row>
@@ -794,44 +794,44 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>81,23%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>81,37%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
           <t>56,49%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>77,6%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>76,07%</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>81,23%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>81,37%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
           <t>69,2%</t>
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>91,87%</t>
+          <t>90,45%</t>
         </is>
       </c>
     </row>
@@ -862,17 +862,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>28,05; 79,42</t>
+          <t>56,47; 94,67</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>45,53; 100,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26,06; 100,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -882,17 +882,17 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>59,51; 94,37</t>
+          <t>28,17; 79,48</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>42,34; 100,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>25,24; 100,0</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -902,17 +902,17 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>50,59; 84,27</t>
+          <t>47,76; 84,09</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>68,32; 100,0</t>
+          <t>68,26; 100,0</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>56,85; 100,0</t>
+          <t>53,05; 100,0</t>
         </is>
       </c>
     </row>
@@ -929,44 +929,44 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>81,27%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>40,18%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>61,24%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>76,22%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>43,54%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>81,27%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>40,18%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>63,92%</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
           <t>78,88%</t>
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>32,72%</t>
+          <t>29,77%</t>
         </is>
       </c>
     </row>
@@ -997,12 +997,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>37,93; 100,0</t>
+          <t>43,28; 100,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>18,76; 69,05</t>
+          <t>19,98; 65,04</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1012,17 +1012,17 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 100,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>41,67; 100,0</t>
+          <t>31,66; 100,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>20,11; 60,74</t>
+          <t>23,86; 68,97</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1032,27 +1032,27 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>56,08; 94,79</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>26,59; 58,33</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
           <t>0,0; 100,0</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>56,02; 94,6</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>27,04; 58,41</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 100,0</t>
-        </is>
-      </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 71,58</t>
+          <t>0,0; 75,55</t>
         </is>
       </c>
     </row>
@@ -1069,44 +1069,44 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>23,32%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>50,88%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>89,56%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>55,95%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>86,97%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>23,32%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>50,88%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>89,56%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
           <t>38,35%</t>
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>31,6%</t>
+          <t>34,7%</t>
         </is>
       </c>
     </row>
@@ -1137,17 +1137,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>24,24; 84,13</t>
+          <t>7,26; 56,47</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>12,29; 100,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>40,46; 100,0</t>
+          <t>55,04; 100,0</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1157,17 +1157,17 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,15; 56,12</t>
+          <t>27,3; 84,42</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,29; 100,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>57,77; 100,0</t>
+          <t>38,12; 100,0</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1177,17 +1177,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>20,08; 60,91</t>
+          <t>20,97; 60,55</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>32,12; 100,0</t>
+          <t>29,39; 100,0</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>59,24; 100,0</t>
+          <t>66,07; 100,0</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>33,04%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>66,99%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>33,04%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16,19; 100,0</t>
+          <t>16,09; 84,29</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1349,42 +1349,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>20,52%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>55,29%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>51,37%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>37,5%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>79,17%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>78,01%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>20,52%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>55,29%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>51,37%</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>78,4%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>86,83%</t>
+          <t>86,28%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 80,08</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9,88; 72,66</t>
+          <t>32,59; 76,24</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>17,82; 100,0</t>
+          <t>14,31; 87,96</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>25,45; 100,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 80,13</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>32,4; 76,67</t>
+          <t>9,76; 68,58</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>13,31; 87,85</t>
+          <t>19,63; 100,0</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>26,05; 100,0</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 58,5</t>
+          <t>0,0; 64,78</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>28,43; 65,89</t>
+          <t>30,56; 68,12</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>31,54; 84,94</t>
+          <t>31,46; 85,07</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>45,19; 100,0</t>
+          <t>39,18; 100,0</t>
         </is>
       </c>
     </row>
@@ -1489,42 +1489,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>76,5%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>48,42%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>84,46%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>76,9%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>60,56%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>34,69%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>89,47%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>76,5%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>48,42%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>84,46%</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>77,29%</t>
+          <t>90,66%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>81,79%</t>
+          <t>81,91%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>29,96; 90,19</t>
+          <t>52,85; 93,78</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>16,36; 58,68</t>
+          <t>30,43; 67,71</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>36,33; 100,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>46,31; 100,0</t>
+          <t>39,22; 100,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>52,86; 93,81</t>
+          <t>30,07; 90,22</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>30,66; 65,85</t>
+          <t>16,4; 59,59</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>35,08; 100,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>39,79; 100,0</t>
+          <t>52,01; 100,0</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>50,24; 85,38</t>
+          <t>51,71; 85,46</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>29,8; 58,41</t>
+          <t>28,33; 57,09</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>61,7; 100,0</t>
+          <t>61,12; 100,0</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>54,19; 95,64</t>
+          <t>53,98; 96,5</t>
         </is>
       </c>
     </row>
@@ -1629,37 +1629,37 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>78,18%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>83,34%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>91,36%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
           <t>83,73%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>67,66%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>84,64%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>78,18%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>83,34%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>91,36%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -1697,17 +1697,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>30,26; 100,0</t>
+          <t>50,05; 94,39</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>33,09; 89,63</t>
+          <t>33,74; 100,0</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>34,74; 100,0</t>
+          <t>63,3; 100,0</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1717,17 +1717,17 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>50,31; 94,17</t>
+          <t>30,3; 100,0</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>33,55; 100,0</t>
+          <t>33,22; 89,81</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>63,81; 100,0</t>
+          <t>35,18; 100,0</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1737,17 +1737,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>55,08; 94,32</t>
+          <t>58,93; 94,9</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>46,28; 93,31</t>
+          <t>47,78; 93,68</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>67,61; 100,0</t>
+          <t>70,0; 100,0</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1769,42 +1769,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>63,68%</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>56,93%</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>74,63%</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>81,09%</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>60,64%</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>49,12%</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>89,39%</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>68,32%</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>63,68%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>56,93%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>74,63%</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>82,08%</t>
+          <t>69,35%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>76,35%</t>
+          <t>75,97%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>46,15; 72,55</t>
+          <t>51,93; 74,21</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>36,98; 60,1</t>
+          <t>46,34; 66,11</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>73,31; 96,93</t>
+          <t>61,69; 84,75</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>47,07; 85,19</t>
+          <t>60,56; 93,45</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>52,74; 74,34</t>
+          <t>47,21; 71,98</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>47,51; 66,18</t>
+          <t>38,36; 60,95</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>61,89; 84,78</t>
+          <t>74,54; 97,15</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>63,09; 93,49</t>
+          <t>48,84; 85,26</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>53,37; 70,18</t>
+          <t>53,35; 70,34</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>46,54; 60,79</t>
+          <t>45,56; 60,72</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>70,74; 87,58</t>
+          <t>69,61; 86,64</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>62,85; 87,16</t>
+          <t>61,46; 85,56</t>
         </is>
       </c>
     </row>
@@ -1957,7 +1957,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1965,7 +1965,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -2073,42 +2073,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -2141,54 +2141,54 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>5095</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>4399</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>3524</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>3007</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>2683</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>1763</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>1422</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>5095</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>1323</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>7778</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>4399</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>3524</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>3804</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>7778</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>4399</t>
-        </is>
-      </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
           <t>5287</t>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5226</t>
+          <t>4330</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>736; 4040</t>
+          <t>2169; 6727</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1991; 5178</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 2380</t>
+          <t>1144; 5521</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 3145</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2610; 6722</t>
+          <t>1210; 4050</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1948; 5178</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1155; 5518</t>
+          <t>508; 2380</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2973</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>4761; 10528</t>
+          <t>4851; 10574</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2134; 5658</t>
+          <t>2088; 5658</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2408; 7526</t>
+          <t>2660; 7680</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2078; 6949</t>
+          <t>1751; 5980</t>
         </is>
       </c>
     </row>
@@ -2281,42 +2281,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -2349,42 +2349,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1341</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>8288</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>5535</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>4753</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>2419</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>5456</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>5353</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2259</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1341</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>8288</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>5535</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>5109</t>
+          <t>2402</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>7368</t>
+          <t>7156</t>
         </is>
       </c>
     </row>
@@ -2422,17 +2422,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2709; 7670</t>
+          <t>5761; 9659</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>3097; 6802</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>758; 2911</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -2442,17 +2442,17 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6072; 9629</t>
+          <t>2721; 7676</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2880; 6802</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>797; 3158</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -2462,17 +2462,17 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>10048; 16737</t>
+          <t>9484; 16701</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8305; 12155</t>
+          <t>8297; 12155</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4559; 8020</t>
+          <t>4197; 7912</t>
         </is>
       </c>
     </row>
@@ -2489,42 +2489,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -2557,44 +2557,44 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>5056</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>5516</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>1020</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>4255</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>4929</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>759</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>5056</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>5516</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>1257</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
           <t>9311</t>
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1257</t>
+          <t>1020</t>
         </is>
       </c>
     </row>
@@ -2625,12 +2625,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2118; 5583</t>
+          <t>2693; 6222</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2124; 7818</t>
+          <t>2743; 8930</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -2640,17 +2640,17 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 1666</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2592; 6222</t>
+          <t>1768; 5583</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2761; 8339</t>
+          <t>2702; 7808</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -2660,17 +2660,17 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 1966</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>6613; 11168</t>
+          <t>6621; 11190</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6772; 14632</t>
+          <t>6661; 14613</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
@@ -2680,7 +2680,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0; 2749</t>
+          <t>0; 2588</t>
         </is>
       </c>
     </row>
@@ -2697,42 +2697,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2765,42 +2765,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1865</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2337</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>7016</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>3822</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>2726</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>4301</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>1865</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>2337</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>7016</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1052</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>946</t>
+          <t>1052</t>
         </is>
       </c>
     </row>
@@ -2833,17 +2833,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1656; 5748</t>
+          <t>580; 4516</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>565; 4593</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2001; 4946</t>
+          <t>4312; 7834</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -2853,17 +2853,17 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>572; 4488</t>
+          <t>1865; 5767</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>565; 4593</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4526; 7834</t>
+          <t>1885; 4946</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2873,22 +2873,22 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2978; 9032</t>
+          <t>3110; 8979</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2351; 7318</t>
+          <t>2150; 7318</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>7571; 12780</t>
+          <t>8444; 12780</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0; 2992</t>
+          <t>0; 3030</t>
         </is>
       </c>
     </row>
@@ -2910,37 +2910,37 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2973,44 +2973,44 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>653</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>1324</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>1083</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>1399</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>605</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="J17" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>653</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>1324</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1043</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>1083</t>
         </is>
       </c>
     </row>
@@ -3046,29 +3046,29 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
+          <t>0; 1975</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
           <t>0; 2089</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>0; 1975</t>
-        </is>
-      </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>658; 4063</t>
+          <t>654; 3425</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
@@ -3113,42 +3113,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -3181,49 +3181,49 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>659</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>7271</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>3069</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>1955</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>2954</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>2807</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>2701</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>2665</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>659</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>7271</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>3069</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>2320</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>659</t>
-        </is>
-      </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
           <t>10226</t>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>5022</t>
+          <t>4621</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2573</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>778; 5724</t>
+          <t>4286; 10027</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>632; 3545</t>
+          <t>855; 5255</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>881; 3462</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 2575</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4261; 10083</t>
+          <t>769; 5402</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>795; 5248</t>
+          <t>696; 3545</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>886; 3400</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 2675</t>
+          <t>0; 2962</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>5979; 13858</t>
+          <t>6428; 14327</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>3002; 8086</t>
+          <t>2995; 8098</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>2613; 5783</t>
+          <t>2099; 5356</t>
         </is>
       </c>
     </row>
@@ -3321,42 +3321,42 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3389,42 +3389,42 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>8936</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>9912</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>3307</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>5271</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>4146</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>4147</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>2663</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>3581</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>8936</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>9912</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>3307</t>
-        </is>
-      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>5285</t>
+          <t>3556</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>8866</t>
+          <t>8826</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2051; 6174</t>
+          <t>6173; 10955</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1956; 7016</t>
+          <t>6229; 13861</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1422; 3915</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1854; 4003</t>
+          <t>2688; 6854</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>6175; 10959</t>
+          <t>2059; 6176</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6276; 13481</t>
+          <t>1961; 7123</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1373; 3915</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>2720; 6837</t>
+          <t>2040; 3922</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>9309; 15819</t>
+          <t>9582; 15833</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>9663; 18942</t>
+          <t>9187; 18515</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>4058; 6578</t>
+          <t>4020; 6578</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>5875; 10367</t>
+          <t>5816; 10398</t>
         </is>
       </c>
     </row>
@@ -3529,37 +3529,37 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="I25" s="2" t="inlineStr">
         <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3597,42 +3597,42 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>6674</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>3396</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>6618</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>954</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
           <t>4082</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>3792</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr">
         <is>
           <t>2639</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>810</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>6674</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>3396</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>6618</t>
-        </is>
-      </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>908</t>
+          <t>919</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>1718</t>
+          <t>1873</t>
         </is>
       </c>
     </row>
@@ -3665,17 +3665,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>1475; 4875</t>
+          <t>4272; 8057</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1855; 5024</t>
+          <t>1375; 4075</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1083; 3118</t>
+          <t>4585; 7244</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -3685,17 +3685,17 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>4294; 8038</t>
+          <t>1477; 4875</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1367; 4075</t>
+          <t>1862; 5034</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>4623; 7244</t>
+          <t>1097; 3118</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3705,17 +3705,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>7387; 12648</t>
+          <t>7903; 12726</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>4480; 9032</t>
+          <t>4625; 9068</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>7005; 10362</t>
+          <t>7253; 10362</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3737,42 +3737,42 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>37</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>18</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -3805,42 +3805,42 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>29626</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>41772</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>30392</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>18044</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
           <t>21408</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>25402</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="I29" s="2" t="inlineStr">
         <is>
           <t>20890</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>11718</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>29626</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>41772</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>30392</t>
-        </is>
-      </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>19726</t>
+          <t>11916</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>31444</t>
+          <t>29960</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>16294; 25613</t>
+          <t>24159; 34526</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>19123; 31080</t>
+          <t>34003; 48513</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>17133; 22651</t>
+          <t>25123; 34515</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>8073; 14610</t>
+          <t>13475; 20795</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>24536; 34588</t>
+          <t>16668; 25410</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>34859; 48560</t>
+          <t>19839; 31517</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>25204; 34525</t>
+          <t>17420; 22702</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>15164; 22468</t>
+          <t>8392; 14651</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>43669; 57426</t>
+          <t>43659; 57555</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>58216; 76037</t>
+          <t>56997; 75948</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>45339; 56135</t>
+          <t>44615; 55531</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>25886; 35896</t>
+          <t>24237; 33742</t>
         </is>
       </c>
     </row>
